--- a/England 2026/prev_tbl.xlsx
+++ b/England 2026/prev_tbl.xlsx
@@ -115,61 +115,61 @@
         <v>25.801989711198452</v>
       </c>
       <c r="J1" s="0">
-        <v>27.671431132758489</v>
+        <v>27.671437396570074</v>
       </c>
       <c r="K1" s="0">
-        <v>28.9843831549959</v>
+        <v>28.984382012090567</v>
       </c>
       <c r="L1" s="0">
-        <v>29.095680626666713</v>
+        <v>29.095677223306012</v>
       </c>
       <c r="M1" s="0">
-        <v>29.096776277998686</v>
+        <v>29.0967738108126</v>
       </c>
       <c r="N1" s="0">
-        <v>29.078220923189342</v>
+        <v>29.078220046668534</v>
       </c>
       <c r="O1" s="0">
-        <v>29.041579672365543</v>
+        <v>29.041580774490413</v>
       </c>
       <c r="P1" s="0">
-        <v>28.991876167713293</v>
+        <v>28.991872780256532</v>
       </c>
       <c r="Q1" s="0">
-        <v>28.934003924808799</v>
+        <v>28.933999699959731</v>
       </c>
       <c r="R1" s="0">
-        <v>28.871864145054989</v>
+        <v>28.871860514478055</v>
       </c>
       <c r="S1" s="0">
-        <v>28.808305136318172</v>
+        <v>28.808302834191121</v>
       </c>
       <c r="T1" s="0">
-        <v>28.745294758236579</v>
+        <v>28.745292765388747</v>
       </c>
       <c r="U1" s="0">
-        <v>28.684114734631574</v>
+        <v>28.684113576506608</v>
       </c>
       <c r="V1" s="0">
-        <v>28.625542688082305</v>
+        <v>28.625542135515722</v>
       </c>
       <c r="W1" s="0">
-        <v>28.569993625893972</v>
+        <v>28.569992905312343</v>
       </c>
       <c r="X1" s="0">
-        <v>28.517629514719026</v>
+        <v>28.517629063330482</v>
       </c>
       <c r="Y1" s="0">
-        <v>28.468444443006416</v>
+        <v>28.468444302840993</v>
       </c>
       <c r="Z1" s="0">
-        <v>28.422324334331542</v>
+        <v>28.422324218819384</v>
       </c>
       <c r="AA1" s="0">
-        <v>28.379090486244511</v>
+        <v>28.379090261755437</v>
       </c>
       <c r="AB1" s="0">
-        <v>28.338530361507647</v>
+        <v>28.33853017332731</v>
       </c>
     </row>
     <row r="2">
@@ -201,61 +201,61 @@
         <v>31.928556550407951</v>
       </c>
       <c r="J2" s="0">
-        <v>33.77375391046025</v>
+        <v>33.773763107886481</v>
       </c>
       <c r="K2" s="0">
-        <v>35.166748919545455</v>
+        <v>35.166742623144827</v>
       </c>
       <c r="L2" s="0">
-        <v>35.336602132248892</v>
+        <v>35.33660155240279</v>
       </c>
       <c r="M2" s="0">
-        <v>35.37354725197752</v>
+        <v>35.373548696283137</v>
       </c>
       <c r="N2" s="0">
-        <v>35.37762810200293</v>
+        <v>35.377629989132771</v>
       </c>
       <c r="O2" s="0">
-        <v>35.355306374323369</v>
+        <v>35.355307286750239</v>
       </c>
       <c r="P2" s="0">
-        <v>35.314145998108522</v>
+        <v>35.314146699548452</v>
       </c>
       <c r="Q2" s="0">
-        <v>35.260666772545214</v>
+        <v>35.260666843930743</v>
       </c>
       <c r="R2" s="0">
-        <v>35.199925040662364</v>
+        <v>35.199924963215217</v>
       </c>
       <c r="S2" s="0">
-        <v>35.135648461718432</v>
+        <v>35.13564842420481</v>
       </c>
       <c r="T2" s="0">
-        <v>35.070480901808324</v>
+        <v>35.070480913081298</v>
       </c>
       <c r="U2" s="0">
-        <v>35.006226540150791</v>
+        <v>35.00622656433449</v>
       </c>
       <c r="V2" s="0">
-        <v>34.944058268021095</v>
+        <v>34.944058291427162</v>
       </c>
       <c r="W2" s="0">
-        <v>34.884687098929128</v>
+        <v>34.884687292479349</v>
       </c>
       <c r="X2" s="0">
-        <v>34.828492636871324</v>
+        <v>34.82849287532256</v>
       </c>
       <c r="Y2" s="0">
-        <v>34.775621629845709</v>
+        <v>34.775621848867189</v>
       </c>
       <c r="Z2" s="0">
-        <v>34.726063534083799</v>
+        <v>34.726063795585823</v>
       </c>
       <c r="AA2" s="0">
-        <v>34.679705402262009</v>
+        <v>34.679705652295667</v>
       </c>
       <c r="AB2" s="0">
-        <v>34.636371452857148</v>
+        <v>34.636371720376502</v>
       </c>
     </row>
     <row r="3">
@@ -287,1351 +287,1351 @@
         <v>39.533977733903953</v>
       </c>
       <c r="J3" s="0">
-        <v>41.300002503869308</v>
+        <v>41.300005003446614</v>
       </c>
       <c r="K3" s="0">
-        <v>42.760197151347207</v>
+        <v>42.760129982481999</v>
       </c>
       <c r="L3" s="0">
-        <v>42.991787537349133</v>
+        <v>42.991787121062664</v>
       </c>
       <c r="M3" s="0">
-        <v>43.06580850555843</v>
+        <v>43.065809228342907</v>
       </c>
       <c r="N3" s="0">
-        <v>43.089833316125017</v>
+        <v>43.089835059255357</v>
       </c>
       <c r="O3" s="0">
-        <v>43.07543411681101</v>
+        <v>43.075434757576275</v>
       </c>
       <c r="P3" s="0">
-        <v>43.033252928939937</v>
+        <v>43.033254797476815</v>
       </c>
       <c r="Q3" s="0">
-        <v>42.971983960253354</v>
+        <v>42.971985096790398</v>
       </c>
       <c r="R3" s="0">
-        <v>42.898351859409047</v>
+        <v>42.898352323766517</v>
       </c>
       <c r="S3" s="0">
-        <v>42.817404103492677</v>
+        <v>42.817404383673711</v>
       </c>
       <c r="T3" s="0">
-        <v>42.732840578666057</v>
+        <v>42.732840640581209</v>
       </c>
       <c r="U3" s="0">
-        <v>42.647310022816662</v>
+        <v>42.647309806661497</v>
       </c>
       <c r="V3" s="0">
-        <v>42.562658412352867</v>
+        <v>42.562658596744392</v>
       </c>
       <c r="W3" s="0">
-        <v>42.480128570980064</v>
+        <v>42.480128955796758</v>
       </c>
       <c r="X3" s="0">
-        <v>42.400514372567699</v>
+        <v>42.400514556321788</v>
       </c>
       <c r="Y3" s="0">
-        <v>42.324281678562635</v>
+        <v>42.324281929751116</v>
       </c>
       <c r="Z3" s="0">
-        <v>42.25166056000154</v>
+        <v>42.251661034206819</v>
       </c>
       <c r="AA3" s="0">
-        <v>42.182715130005249</v>
+        <v>42.182715714101022</v>
       </c>
       <c r="AB3" s="0">
-        <v>42.117395370478178</v>
+        <v>42.117395927926971</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>30.861929429879801</v>
+        <v>37.683337917498449</v>
       </c>
       <c r="B4" s="0">
-        <v>38.510576265421427</v>
+        <v>35.400571542032573</v>
       </c>
       <c r="C4" s="0">
-        <v>47.74400348287552</v>
+        <v>33.103073730970891</v>
       </c>
       <c r="D4" s="0">
-        <v>33.565244618504586</v>
+        <v>30.861929556563393</v>
       </c>
       <c r="E4" s="0">
-        <v>31.473904670803133</v>
+        <v>28.928915608686307</v>
       </c>
       <c r="F4" s="0">
-        <v>29.836865431113235</v>
+        <v>27.423305541630615</v>
       </c>
       <c r="G4" s="0">
-        <v>28.377819701122913</v>
+        <v>26.063131162241565</v>
       </c>
       <c r="H4" s="0">
-        <v>27.43406174055001</v>
+        <v>25.205593701152637</v>
       </c>
       <c r="I4" s="0">
-        <v>27.88262141718684</v>
+        <v>25.801989711198452</v>
       </c>
       <c r="J4" s="0">
-        <v>29.58408386692367</v>
+        <v>27.671437396570074</v>
       </c>
       <c r="K4" s="0">
-        <v>30.840204988194199</v>
+        <v>28.984382012090567</v>
       </c>
       <c r="L4" s="0">
-        <v>31.050654175000563</v>
+        <v>29.095677223306012</v>
       </c>
       <c r="M4" s="0">
-        <v>31.13356700217944</v>
+        <v>29.0967738108126</v>
       </c>
       <c r="N4" s="0">
-        <v>31.175187058009147</v>
+        <v>29.078220829858832</v>
       </c>
       <c r="O4" s="0">
-        <v>31.172251095266645</v>
+        <v>29.028739085921696</v>
       </c>
       <c r="P4" s="0">
-        <v>31.084992526799233</v>
+        <v>28.90766932239222</v>
       </c>
       <c r="Q4" s="0">
-        <v>30.89177370635176</v>
+        <v>28.69418469035325</v>
       </c>
       <c r="R4" s="0">
-        <v>30.593471431813374</v>
+        <v>28.388569152902111</v>
       </c>
       <c r="S4" s="0">
-        <v>30.204892887646473</v>
+        <v>28.00408198551224</v>
       </c>
       <c r="T4" s="0">
-        <v>29.747889047692134</v>
+        <v>27.560516657892094</v>
       </c>
       <c r="U4" s="0">
-        <v>29.2461265155181</v>
+        <v>27.07937328940967</v>
       </c>
       <c r="V4" s="0">
-        <v>28.721582729567548</v>
+        <v>26.580598309708119</v>
       </c>
       <c r="W4" s="0">
-        <v>28.199137561386493</v>
+        <v>26.087364590226631</v>
       </c>
       <c r="X4" s="0">
-        <v>27.712776647103457</v>
+        <v>25.630813171303128</v>
       </c>
       <c r="Y4" s="0">
-        <v>27.278247793868506</v>
+        <v>25.224194518453302</v>
       </c>
       <c r="Z4" s="0">
-        <v>26.898198526543865</v>
+        <v>24.869131289119565</v>
       </c>
       <c r="AA4" s="0">
-        <v>26.569222840411843</v>
+        <v>24.56194780991159</v>
       </c>
       <c r="AB4" s="0">
-        <v>26.285485511761092</v>
+        <v>24.296905850336515</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>28.928915489756044</v>
+        <v>46.351282985848357</v>
       </c>
       <c r="B5" s="0">
-        <v>36.205261741629798</v>
+        <v>43.764925173661794</v>
       </c>
       <c r="C5" s="0">
-        <v>45.090495707584481</v>
+        <v>41.123488317495223</v>
       </c>
       <c r="D5" s="0">
-        <v>41.20888822405874</v>
+        <v>38.510576210699163</v>
       </c>
       <c r="E5" s="0">
-        <v>38.830695302346996</v>
+        <v>36.205261583571499</v>
       </c>
       <c r="F5" s="0">
-        <v>36.908102291564838</v>
+        <v>34.354622197488254</v>
       </c>
       <c r="G5" s="0">
-        <v>35.167775912987288</v>
+        <v>32.675601816306042</v>
       </c>
       <c r="H5" s="0">
-        <v>33.952432071429953</v>
+        <v>31.527029181394987</v>
       </c>
       <c r="I5" s="0">
-        <v>34.240968730004724</v>
+        <v>31.928556550407951</v>
       </c>
       <c r="J5" s="0">
-        <v>35.981644453177864</v>
+        <v>33.773763107886481</v>
       </c>
       <c r="K5" s="0">
-        <v>37.416258318344987</v>
+        <v>35.166742623144827</v>
       </c>
       <c r="L5" s="0">
-        <v>37.528077338803236</v>
+        <v>35.33660155240279</v>
       </c>
       <c r="M5" s="0">
-        <v>37.535062996737239</v>
+        <v>35.373548696283137</v>
       </c>
       <c r="N5" s="0">
-        <v>37.516593002900564</v>
+        <v>35.377630723300655</v>
       </c>
       <c r="O5" s="0">
-        <v>37.480168725955266</v>
+        <v>35.340953363984312</v>
       </c>
       <c r="P5" s="0">
-        <v>37.408718167507935</v>
+        <v>35.218675435917426</v>
       </c>
       <c r="Q5" s="0">
-        <v>37.2088111093762</v>
+        <v>34.985956368394184</v>
       </c>
       <c r="R5" s="0">
-        <v>36.880464459257404</v>
+        <v>34.641600512479322</v>
       </c>
       <c r="S5" s="0">
-        <v>36.439631748802803</v>
+        <v>34.199536329941608</v>
       </c>
       <c r="T5" s="0">
-        <v>35.910731685400109</v>
+        <v>33.681742911582234</v>
       </c>
       <c r="U5" s="0">
-        <v>35.344583477841979</v>
+        <v>33.11277060735604</v>
       </c>
       <c r="V5" s="0">
-        <v>34.77204933995921</v>
+        <v>32.515939984592393</v>
       </c>
       <c r="W5" s="0">
-        <v>34.193046824591413</v>
+        <v>31.918458225090184</v>
       </c>
       <c r="X5" s="0">
-        <v>33.641382651437262</v>
+        <v>31.357279205294507</v>
       </c>
       <c r="Y5" s="0">
-        <v>33.134579079350594</v>
+        <v>30.84986110776407</v>
       </c>
       <c r="Z5" s="0">
-        <v>32.677970597157646</v>
+        <v>30.400141708962785</v>
       </c>
       <c r="AA5" s="0">
-        <v>32.270761484137779</v>
+        <v>30.005554585149191</v>
       </c>
       <c r="AB5" s="0">
-        <v>31.909280635954584</v>
+        <v>29.660718283167032</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>27.423305429685996</v>
+        <v>56.428959806049726</v>
       </c>
       <c r="B6" s="0">
-        <v>34.354622321211664</v>
+        <v>53.606561742358551</v>
       </c>
       <c r="C6" s="0">
-        <v>42.88907753811975</v>
+        <v>50.680813812558284</v>
       </c>
       <c r="D6" s="0">
-        <v>58.678480244564689</v>
+        <v>47.744003987371933</v>
       </c>
       <c r="E6" s="0">
-        <v>55.790058848714153</v>
+        <v>45.090496277587995</v>
       </c>
       <c r="F6" s="0">
-        <v>53.306451851318258</v>
+        <v>42.889078061999882</v>
       </c>
       <c r="G6" s="0">
-        <v>50.997547755721989</v>
+        <v>40.863186783620286</v>
       </c>
       <c r="H6" s="0">
-        <v>49.18680524046146</v>
+        <v>39.37556043289932</v>
       </c>
       <c r="I6" s="0">
-        <v>48.818985038749489</v>
+        <v>39.533977733903953</v>
       </c>
       <c r="J6" s="0">
-        <v>49.892425513627138</v>
+        <v>41.300005003446614</v>
       </c>
       <c r="K6" s="0">
-        <v>50.795212376069358</v>
+        <v>42.760129982481999</v>
       </c>
       <c r="L6" s="0">
-        <v>50.75972414013193</v>
+        <v>42.991787121062664</v>
       </c>
       <c r="M6" s="0">
-        <v>50.631770892138903</v>
+        <v>43.065809228342907</v>
       </c>
       <c r="N6" s="0">
-        <v>50.492213374692497</v>
+        <v>43.089835499880323</v>
       </c>
       <c r="O6" s="0">
-        <v>50.332899122243276</v>
+        <v>43.059300724558526</v>
       </c>
       <c r="P6" s="0">
-        <v>50.107010668804335</v>
+        <v>42.924779658257087</v>
       </c>
       <c r="Q6" s="0">
-        <v>49.783089348192654</v>
+        <v>42.657239186092042</v>
       </c>
       <c r="R6" s="0">
-        <v>49.352265262873367</v>
+        <v>42.253982862049277</v>
       </c>
       <c r="S6" s="0">
-        <v>48.821478047623742</v>
+        <v>41.729747406253864</v>
       </c>
       <c r="T6" s="0">
-        <v>48.207276710190101</v>
+        <v>41.108987163723725</v>
       </c>
       <c r="U6" s="0">
-        <v>47.530642223113922</v>
+        <v>40.419725667935964</v>
       </c>
       <c r="V6" s="0">
-        <v>46.813139795969121</v>
+        <v>39.689196816982985</v>
       </c>
       <c r="W6" s="0">
-        <v>46.081038310819686</v>
+        <v>38.949402490236224</v>
       </c>
       <c r="X6" s="0">
-        <v>45.37189778483998</v>
+        <v>38.244191310222895</v>
       </c>
       <c r="Y6" s="0">
-        <v>44.706974981251541</v>
+        <v>37.596129922222161</v>
       </c>
       <c r="Z6" s="0">
-        <v>44.094468449669591</v>
+        <v>37.01223704645701</v>
       </c>
       <c r="AA6" s="0">
-        <v>43.535685626535432</v>
+        <v>36.491690101985405</v>
       </c>
       <c r="AB6" s="0">
-        <v>43.028446074543616</v>
+        <v>36.029975708417737</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>26.063135021314505</v>
+        <v>37.683337917498449</v>
       </c>
       <c r="B7" s="0">
-        <v>32.675602182873881</v>
+        <v>35.400571542032573</v>
       </c>
       <c r="C7" s="0">
-        <v>40.863183144477127</v>
+        <v>33.103073730970891</v>
       </c>
       <c r="D7" s="0">
-        <v>33.565244618504586</v>
+        <v>30.861929556563393</v>
       </c>
       <c r="E7" s="0">
-        <v>31.473904670803133</v>
+        <v>28.928915608686307</v>
       </c>
       <c r="F7" s="0">
-        <v>29.836865431113235</v>
+        <v>27.423305541630615</v>
       </c>
       <c r="G7" s="0">
-        <v>28.377819701122913</v>
+        <v>26.063131162241565</v>
       </c>
       <c r="H7" s="0">
-        <v>27.43406174055001</v>
+        <v>25.205593701152637</v>
       </c>
       <c r="I7" s="0">
-        <v>27.88262141718684</v>
+        <v>25.801989711198452</v>
       </c>
       <c r="J7" s="0">
-        <v>29.58408386692367</v>
+        <v>27.671437396570074</v>
       </c>
       <c r="K7" s="0">
-        <v>30.840204988194199</v>
+        <v>28.984382012090567</v>
       </c>
       <c r="L7" s="0">
-        <v>31.050654175000563</v>
+        <v>29.095677223306012</v>
       </c>
       <c r="M7" s="0">
-        <v>31.13356700217944</v>
+        <v>29.0967738108126</v>
       </c>
       <c r="N7" s="0">
-        <v>31.175187057898885</v>
+        <v>29.078220829677292</v>
       </c>
       <c r="O7" s="0">
-        <v>31.172077466754107</v>
+        <v>29.028570450313492</v>
       </c>
       <c r="P7" s="0">
-        <v>31.08418611694993</v>
+        <v>28.906891415254911</v>
       </c>
       <c r="Q7" s="0">
-        <v>30.890065525661228</v>
+        <v>28.692546896275061</v>
       </c>
       <c r="R7" s="0">
-        <v>30.590798086352017</v>
+        <v>28.386020585291522</v>
       </c>
       <c r="S7" s="0">
-        <v>30.201327409518648</v>
+        <v>28.000700883176442</v>
       </c>
       <c r="T7" s="0">
-        <v>29.74358648716391</v>
+        <v>27.556456802910905</v>
       </c>
       <c r="U7" s="0">
-        <v>29.241286782906666</v>
+        <v>27.074828248485719</v>
       </c>
       <c r="V7" s="0">
-        <v>28.716425755366966</v>
+        <v>26.5757780216831</v>
       </c>
       <c r="W7" s="0">
-        <v>28.194061767136471</v>
+        <v>26.082648595213243</v>
       </c>
       <c r="X7" s="0">
-        <v>27.708462278222278</v>
+        <v>25.626846537454178</v>
       </c>
       <c r="Y7" s="0">
-        <v>27.275157602417881</v>
+        <v>25.221406824220136</v>
       </c>
       <c r="Z7" s="0">
-        <v>26.896560494473309</v>
+        <v>24.867725853300851</v>
       </c>
       <c r="AA7" s="0">
-        <v>26.569113009169541</v>
+        <v>24.561984704112913</v>
       </c>
       <c r="AB7" s="0">
-        <v>26.286893200896095</v>
+        <v>24.298365348337786</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>25.205596003577771</v>
+        <v>46.351282985848357</v>
       </c>
       <c r="B8" s="0">
-        <v>31.527025856007445</v>
+        <v>43.764925173661794</v>
       </c>
       <c r="C8" s="0">
-        <v>39.375561158767553</v>
+        <v>41.123488317495223</v>
       </c>
       <c r="D8" s="0">
-        <v>41.20888822405874</v>
+        <v>38.510576210699163</v>
       </c>
       <c r="E8" s="0">
-        <v>38.830695302346996</v>
+        <v>36.205261583571499</v>
       </c>
       <c r="F8" s="0">
-        <v>36.908102291564838</v>
+        <v>34.354622197488254</v>
       </c>
       <c r="G8" s="0">
-        <v>35.167775912987288</v>
+        <v>32.675601816306042</v>
       </c>
       <c r="H8" s="0">
-        <v>33.952432071429953</v>
+        <v>31.527029181394987</v>
       </c>
       <c r="I8" s="0">
-        <v>34.240968730004724</v>
+        <v>31.928556550407951</v>
       </c>
       <c r="J8" s="0">
-        <v>35.981644453177864</v>
+        <v>33.773763107886481</v>
       </c>
       <c r="K8" s="0">
-        <v>37.416258318344987</v>
+        <v>35.166742623144827</v>
       </c>
       <c r="L8" s="0">
-        <v>37.528077338803236</v>
+        <v>35.33660155240279</v>
       </c>
       <c r="M8" s="0">
-        <v>37.535062996737239</v>
+        <v>35.373548696283137</v>
       </c>
       <c r="N8" s="0">
-        <v>37.516593000536211</v>
+        <v>35.377630722452338</v>
       </c>
       <c r="O8" s="0">
-        <v>37.480018074335511</v>
+        <v>35.340798941431508</v>
       </c>
       <c r="P8" s="0">
-        <v>37.408009826983012</v>
+        <v>35.217954994577376</v>
       </c>
       <c r="Q8" s="0">
-        <v>37.207291025314099</v>
+        <v>34.984420756419837</v>
       </c>
       <c r="R8" s="0">
-        <v>36.878054124109084</v>
+        <v>34.639181326019063</v>
       </c>
       <c r="S8" s="0">
-        <v>36.436374217604218</v>
+        <v>34.196286959015495</v>
       </c>
       <c r="T8" s="0">
-        <v>35.906747259582374</v>
+        <v>33.677791797939214</v>
       </c>
       <c r="U8" s="0">
-        <v>35.340151933079035</v>
+        <v>33.108289119291833</v>
       </c>
       <c r="V8" s="0">
-        <v>34.76723402650142</v>
+        <v>32.511120704284615</v>
       </c>
       <c r="W8" s="0">
-        <v>34.188184922545368</v>
+        <v>31.913655328834352</v>
       </c>
       <c r="X8" s="0">
-        <v>33.637065917852176</v>
+        <v>31.353103711700438</v>
       </c>
       <c r="Y8" s="0">
-        <v>33.131239640189769</v>
+        <v>30.846740233530451</v>
       </c>
       <c r="Z8" s="0">
-        <v>32.675853838307937</v>
+        <v>30.398297771705963</v>
       </c>
       <c r="AA8" s="0">
-        <v>32.269984179207526</v>
+        <v>30.005074459337745</v>
       </c>
       <c r="AB8" s="0">
-        <v>31.909880151802611</v>
+        <v>29.661609118796964</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>25.801991580233615</v>
+        <v>56.428959806049726</v>
       </c>
       <c r="B9" s="0">
-        <v>31.928556298181526</v>
+        <v>53.606561742358551</v>
       </c>
       <c r="C9" s="0">
-        <v>39.533977179949865</v>
+        <v>50.680813812558284</v>
       </c>
       <c r="D9" s="0">
-        <v>58.678480244564689</v>
+        <v>47.744003987371933</v>
       </c>
       <c r="E9" s="0">
-        <v>55.790058848714153</v>
+        <v>45.090496277587995</v>
       </c>
       <c r="F9" s="0">
-        <v>53.306451851318258</v>
+        <v>42.889078061999882</v>
       </c>
       <c r="G9" s="0">
-        <v>50.997547755721989</v>
+        <v>40.863186783620286</v>
       </c>
       <c r="H9" s="0">
-        <v>49.18680524046146</v>
+        <v>39.37556043289932</v>
       </c>
       <c r="I9" s="0">
-        <v>48.818985038749489</v>
+        <v>39.533977733903953</v>
       </c>
       <c r="J9" s="0">
-        <v>49.892425513627138</v>
+        <v>41.300005003446614</v>
       </c>
       <c r="K9" s="0">
-        <v>50.795212376069358</v>
+        <v>42.760129982481999</v>
       </c>
       <c r="L9" s="0">
-        <v>50.75972414013193</v>
+        <v>42.991787121062664</v>
       </c>
       <c r="M9" s="0">
-        <v>50.631770892138903</v>
+        <v>43.065809228342907</v>
       </c>
       <c r="N9" s="0">
-        <v>50.492213374532938</v>
+        <v>43.089835499385266</v>
       </c>
       <c r="O9" s="0">
-        <v>50.332820146316536</v>
+        <v>43.059172343994206</v>
       </c>
       <c r="P9" s="0">
-        <v>50.106633175445921</v>
+        <v>42.924173228522015</v>
       </c>
       <c r="Q9" s="0">
-        <v>49.782264712439741</v>
+        <v>42.655930352675782</v>
       </c>
       <c r="R9" s="0">
-        <v>49.350933191253979</v>
+        <v>42.251894352967206</v>
       </c>
       <c r="S9" s="0">
-        <v>48.819642469078495</v>
+        <v>41.726905186078049</v>
       </c>
       <c r="T9" s="0">
-        <v>48.20498495620182</v>
+        <v>41.105484094454503</v>
       </c>
       <c r="U9" s="0">
-        <v>47.527970133092047</v>
+        <v>40.415695912630078</v>
       </c>
       <c r="V9" s="0">
-        <v>46.810181256291415</v>
+        <v>39.684797966264156</v>
       </c>
       <c r="W9" s="0">
-        <v>46.077977931469519</v>
+        <v>38.944932126877966</v>
       </c>
       <c r="X9" s="0">
-        <v>45.369070304198871</v>
+        <v>38.240172893100713</v>
       </c>
       <c r="Y9" s="0">
-        <v>44.704641241305751</v>
+        <v>37.592947125416572</v>
       </c>
       <c r="Z9" s="0">
-        <v>44.092792697902731</v>
+        <v>37.010107862099353</v>
       </c>
       <c r="AA9" s="0">
-        <v>43.53476238573397</v>
+        <v>36.490718535075217</v>
       </c>
       <c r="AB9" s="0">
-        <v>43.028324145548027</v>
+        <v>36.030195069297307</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>27.671435541984888</v>
+        <v>37.683337917498449</v>
       </c>
       <c r="B10" s="0">
-        <v>33.773752358632855</v>
+        <v>35.400571542032573</v>
       </c>
       <c r="C10" s="0">
-        <v>41.299997487531783</v>
+        <v>33.103073730970891</v>
       </c>
       <c r="D10" s="0">
-        <v>33.565244618504586</v>
+        <v>30.861929556563393</v>
       </c>
       <c r="E10" s="0">
-        <v>31.473904670803133</v>
+        <v>28.928915608686307</v>
       </c>
       <c r="F10" s="0">
-        <v>29.836865431113235</v>
+        <v>27.423305541630615</v>
       </c>
       <c r="G10" s="0">
-        <v>28.377819701122913</v>
+        <v>26.063131162241565</v>
       </c>
       <c r="H10" s="0">
-        <v>27.43406174055001</v>
+        <v>25.205593701152637</v>
       </c>
       <c r="I10" s="0">
-        <v>27.88262141718684</v>
+        <v>25.801989711198452</v>
       </c>
       <c r="J10" s="0">
-        <v>29.58408386692367</v>
+        <v>27.671437396570074</v>
       </c>
       <c r="K10" s="0">
-        <v>30.840204988194199</v>
+        <v>28.984382012090567</v>
       </c>
       <c r="L10" s="0">
-        <v>31.050654175000563</v>
+        <v>29.095677223306012</v>
       </c>
       <c r="M10" s="0">
-        <v>31.13356700217944</v>
+        <v>29.0967738108126</v>
       </c>
       <c r="N10" s="0">
-        <v>31.175182148831588</v>
+        <v>29.078213150658176</v>
       </c>
       <c r="O10" s="0">
-        <v>30.786438581180875</v>
+        <v>28.664018927748341</v>
       </c>
       <c r="P10" s="0">
-        <v>29.720512049378325</v>
+        <v>27.626443770967377</v>
       </c>
       <c r="Q10" s="0">
-        <v>28.187869005396479</v>
+        <v>26.169905621138454</v>
       </c>
       <c r="R10" s="0">
-        <v>26.378935451489181</v>
+        <v>24.47241948859995</v>
       </c>
       <c r="S10" s="0">
-        <v>24.454243543063811</v>
+        <v>22.680510117029734</v>
       </c>
       <c r="T10" s="0">
-        <v>22.537336140458088</v>
+        <v>20.905127807795513</v>
       </c>
       <c r="U10" s="0">
-        <v>20.713554967650815</v>
+        <v>19.221870094926455</v>
       </c>
       <c r="V10" s="0">
-        <v>19.033920455051572</v>
+        <v>17.675193796304228</v>
       </c>
       <c r="W10" s="0">
-        <v>17.712114043204313</v>
+        <v>16.465541327446555</v>
       </c>
       <c r="X10" s="0">
-        <v>16.794042908498152</v>
+        <v>15.632398380674774</v>
       </c>
       <c r="Y10" s="0">
-        <v>16.134524210837007</v>
+        <v>15.036296514289107</v>
       </c>
       <c r="Z10" s="0">
-        <v>15.648333701951545</v>
+        <v>14.597567773078055</v>
       </c>
       <c r="AA10" s="0">
-        <v>15.281902798287192</v>
+        <v>14.267021794313319</v>
       </c>
       <c r="AB10" s="0">
-        <v>14.999981862301459</v>
+        <v>14.012576560466322</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>28.984386640678054</v>
+        <v>46.351282985848357</v>
       </c>
       <c r="B11" s="0">
-        <v>35.166744711520202</v>
+        <v>43.764925173661794</v>
       </c>
       <c r="C11" s="0">
-        <v>42.760193069216754</v>
+        <v>41.123488317495223</v>
       </c>
       <c r="D11" s="0">
-        <v>41.20888822405874</v>
+        <v>38.510576210699163</v>
       </c>
       <c r="E11" s="0">
-        <v>38.830695302346996</v>
+        <v>36.205261583571499</v>
       </c>
       <c r="F11" s="0">
-        <v>36.908102291564838</v>
+        <v>34.354622197488254</v>
       </c>
       <c r="G11" s="0">
-        <v>35.167775912987288</v>
+        <v>32.675601816306042</v>
       </c>
       <c r="H11" s="0">
-        <v>33.952432071429953</v>
+        <v>31.527029181394987</v>
       </c>
       <c r="I11" s="0">
-        <v>34.240968730004724</v>
+        <v>31.928556550407951</v>
       </c>
       <c r="J11" s="0">
-        <v>35.981644453177864</v>
+        <v>33.773763107886481</v>
       </c>
       <c r="K11" s="0">
-        <v>37.416258318344987</v>
+        <v>35.166742623144827</v>
       </c>
       <c r="L11" s="0">
-        <v>37.528077338803236</v>
+        <v>35.33660155240279</v>
       </c>
       <c r="M11" s="0">
-        <v>37.535062996737239</v>
+        <v>35.373548696283137</v>
       </c>
       <c r="N11" s="0">
-        <v>37.516517936448878</v>
+        <v>35.377597605855748</v>
       </c>
       <c r="O11" s="0">
-        <v>37.003583727208643</v>
+        <v>34.894722924922967</v>
       </c>
       <c r="P11" s="0">
-        <v>35.701236927219277</v>
+        <v>33.631116968343669</v>
       </c>
       <c r="Q11" s="0">
-        <v>33.789280429636527</v>
+        <v>31.825780429517788</v>
       </c>
       <c r="R11" s="0">
-        <v>31.504713075496916</v>
+        <v>29.69822127560526</v>
       </c>
       <c r="S11" s="0">
-        <v>29.055029313267166</v>
+        <v>27.435758933899663</v>
       </c>
       <c r="T11" s="0">
-        <v>26.604763376350739</v>
+        <v>25.184140066487533</v>
       </c>
       <c r="U11" s="0">
-        <v>24.270531557044059</v>
+        <v>23.045004922052836</v>
       </c>
       <c r="V11" s="0">
-        <v>22.123863075388005</v>
+        <v>21.079531520061458</v>
       </c>
       <c r="W11" s="0">
-        <v>20.421854676299713</v>
+        <v>19.528470372658543</v>
       </c>
       <c r="X11" s="0">
-        <v>19.221597175059713</v>
+        <v>18.442371841353403</v>
       </c>
       <c r="Y11" s="0">
-        <v>18.348622418608844</v>
+        <v>17.630753205770699</v>
       </c>
       <c r="Z11" s="0">
-        <v>17.669886291057573</v>
+        <v>17.020759920482881</v>
       </c>
       <c r="AA11" s="0">
-        <v>17.151106421316385</v>
+        <v>16.555164034346575</v>
       </c>
       <c r="AB11" s="0">
-        <v>16.747361233570697</v>
+        <v>16.193013121352323</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>29.095680947433046</v>
+        <v>56.428959806049726</v>
       </c>
       <c r="B12" s="0">
-        <v>35.336598450859526</v>
+        <v>53.606561742358551</v>
       </c>
       <c r="C12" s="0">
-        <v>42.991783101216051</v>
+        <v>50.680813812558284</v>
       </c>
       <c r="D12" s="0">
-        <v>58.678480244564689</v>
+        <v>47.744003987371933</v>
       </c>
       <c r="E12" s="0">
-        <v>55.790058848714153</v>
+        <v>45.090496277587995</v>
       </c>
       <c r="F12" s="0">
-        <v>53.306451851318258</v>
+        <v>42.889078061999882</v>
       </c>
       <c r="G12" s="0">
-        <v>50.997547755721989</v>
+        <v>40.863186783620286</v>
       </c>
       <c r="H12" s="0">
-        <v>49.18680524046146</v>
+        <v>39.37556043289932</v>
       </c>
       <c r="I12" s="0">
-        <v>48.818985038749489</v>
+        <v>39.533977733903953</v>
       </c>
       <c r="J12" s="0">
-        <v>49.892425513627138</v>
+        <v>41.300005003446614</v>
       </c>
       <c r="K12" s="0">
-        <v>50.795212376069358</v>
+        <v>42.760129982481999</v>
       </c>
       <c r="L12" s="0">
-        <v>50.75972414013193</v>
+        <v>42.991787121062664</v>
       </c>
       <c r="M12" s="0">
-        <v>50.631770892138903</v>
+        <v>43.065809228342907</v>
       </c>
       <c r="N12" s="0">
-        <v>50.492199452003661</v>
+        <v>43.08981248440579</v>
       </c>
       <c r="O12" s="0">
-        <v>49.679251135023712</v>
+        <v>42.507475108265503</v>
       </c>
       <c r="P12" s="0">
-        <v>47.720853497907442</v>
+        <v>40.936708791136439</v>
       </c>
       <c r="Q12" s="0">
-        <v>44.926637389555793</v>
+        <v>38.657897984518265</v>
       </c>
       <c r="R12" s="0">
-        <v>41.610009801378261</v>
+        <v>35.943426119903492</v>
       </c>
       <c r="S12" s="0">
-        <v>38.05781166444428</v>
+        <v>33.035391416973127</v>
       </c>
       <c r="T12" s="0">
-        <v>34.506306685205367</v>
+        <v>30.128408529453957</v>
       </c>
       <c r="U12" s="0">
-        <v>31.128814838069054</v>
+        <v>27.362153857923555</v>
       </c>
       <c r="V12" s="0">
-        <v>28.035155017906476</v>
+        <v>24.823205301713141</v>
       </c>
       <c r="W12" s="0">
-        <v>25.554927808778714</v>
+        <v>22.801455845297827</v>
       </c>
       <c r="X12" s="0">
-        <v>23.758681012787175</v>
+        <v>21.35955759960428</v>
       </c>
       <c r="Y12" s="0">
-        <v>22.422488185247296</v>
+        <v>20.300647315426939</v>
       </c>
       <c r="Z12" s="0">
-        <v>21.406339247550758</v>
+        <v>19.504805748846717</v>
       </c>
       <c r="AA12" s="0">
-        <v>20.618548667965765</v>
+        <v>18.894751995619991</v>
       </c>
       <c r="AB12" s="0">
-        <v>19.99697619201401</v>
+        <v>18.418605598339635</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>29.096777439231165</v>
+        <v>37.683337917498449</v>
       </c>
       <c r="B13" s="0">
-        <v>35.373543769361852</v>
+        <v>35.400571542032573</v>
       </c>
       <c r="C13" s="0">
-        <v>43.065803978270253</v>
+        <v>33.103073730970891</v>
       </c>
       <c r="D13" s="0">
-        <v>33.565244618504586</v>
+        <v>30.861929556563393</v>
       </c>
       <c r="E13" s="0">
-        <v>31.473904670803133</v>
+        <v>28.928915608686307</v>
       </c>
       <c r="F13" s="0">
-        <v>29.836865431113235</v>
+        <v>27.423305541630615</v>
       </c>
       <c r="G13" s="0">
-        <v>28.377819701122913</v>
+        <v>26.063131162241565</v>
       </c>
       <c r="H13" s="0">
-        <v>27.43406174055001</v>
+        <v>25.205593701152637</v>
       </c>
       <c r="I13" s="0">
-        <v>27.88262141718684</v>
+        <v>25.801989711198452</v>
       </c>
       <c r="J13" s="0">
-        <v>29.58408386692367</v>
+        <v>27.671437396570074</v>
       </c>
       <c r="K13" s="0">
-        <v>30.840204988194199</v>
+        <v>28.984382012090567</v>
       </c>
       <c r="L13" s="0">
-        <v>31.050654175000563</v>
+        <v>29.095677223306012</v>
       </c>
       <c r="M13" s="0">
-        <v>31.13356700217944</v>
+        <v>29.0967738108126</v>
       </c>
       <c r="N13" s="0">
-        <v>31.17518075697194</v>
+        <v>29.078211151582874</v>
       </c>
       <c r="O13" s="0">
-        <v>30.67731205261634</v>
+        <v>28.569778299186712</v>
       </c>
       <c r="P13" s="0">
-        <v>29.340527772797522</v>
+        <v>27.299527273684262</v>
       </c>
       <c r="Q13" s="0">
-        <v>27.448289641571879</v>
+        <v>25.535559349487901</v>
       </c>
       <c r="R13" s="0">
-        <v>25.249167799932113</v>
+        <v>23.505503988112881</v>
       </c>
       <c r="S13" s="0">
-        <v>22.947338559328394</v>
+        <v>21.392526605372236</v>
       </c>
       <c r="T13" s="0">
-        <v>20.69577692251335</v>
+        <v>19.332003410796251</v>
       </c>
       <c r="U13" s="0">
-        <v>18.596235890203129</v>
+        <v>17.413026695672052</v>
       </c>
       <c r="V13" s="0">
-        <v>16.70535102430453</v>
+        <v>15.684606068780976</v>
       </c>
       <c r="W13" s="0">
-        <v>15.278046968565331</v>
+        <v>14.383738820641039</v>
       </c>
       <c r="X13" s="0">
-        <v>14.35232472915464</v>
+        <v>13.543415234656297</v>
       </c>
       <c r="Y13" s="0">
-        <v>13.73440684902198</v>
+        <v>12.982130977141546</v>
       </c>
       <c r="Z13" s="0">
-        <v>13.312145735661332</v>
+        <v>12.597181875290929</v>
       </c>
       <c r="AA13" s="0">
-        <v>13.017115555520316</v>
+        <v>12.326730975011314</v>
       </c>
       <c r="AB13" s="0">
-        <v>12.806125609711726</v>
+        <v>12.131786330731428</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>29.078221474800962</v>
+        <v>46.351282985848357</v>
       </c>
       <c r="B14" s="0">
-        <v>35.377624874790811</v>
+        <v>43.764925173661794</v>
       </c>
       <c r="C14" s="0">
-        <v>43.089828863383588</v>
+        <v>41.123488317495223</v>
       </c>
       <c r="D14" s="0">
-        <v>41.20888822405874</v>
+        <v>38.510576210699163</v>
       </c>
       <c r="E14" s="0">
-        <v>38.830695302346996</v>
+        <v>36.205261583571499</v>
       </c>
       <c r="F14" s="0">
-        <v>36.908102291564838</v>
+        <v>34.354622197488254</v>
       </c>
       <c r="G14" s="0">
-        <v>35.167775912987288</v>
+        <v>32.675601816306042</v>
       </c>
       <c r="H14" s="0">
-        <v>33.952432071429953</v>
+        <v>31.527029181394987</v>
       </c>
       <c r="I14" s="0">
-        <v>34.240968730004724</v>
+        <v>31.928556550407951</v>
       </c>
       <c r="J14" s="0">
-        <v>35.981644453177864</v>
+        <v>33.773763107886481</v>
       </c>
       <c r="K14" s="0">
-        <v>37.416258318344987</v>
+        <v>35.166742623144827</v>
       </c>
       <c r="L14" s="0">
-        <v>37.528077338803236</v>
+        <v>35.33660155240279</v>
       </c>
       <c r="M14" s="0">
-        <v>37.535062996737239</v>
+        <v>35.373548696283137</v>
       </c>
       <c r="N14" s="0">
-        <v>37.516496589297084</v>
+        <v>35.377588565956799</v>
       </c>
       <c r="O14" s="0">
-        <v>36.875978221339054</v>
+        <v>34.774066927013742</v>
       </c>
       <c r="P14" s="0">
-        <v>35.251568702911435</v>
+        <v>33.207834574098989</v>
       </c>
       <c r="Q14" s="0">
-        <v>32.905181974402204</v>
+        <v>30.996725862582366</v>
       </c>
       <c r="R14" s="0">
-        <v>30.142561228278076</v>
+        <v>28.424724094943851</v>
       </c>
       <c r="S14" s="0">
-        <v>27.225169030082874</v>
+        <v>25.728785761917866</v>
       </c>
       <c r="T14" s="0">
-        <v>24.35575394440297</v>
+        <v>23.089189987124161</v>
       </c>
       <c r="U14" s="0">
-        <v>21.662393206361454</v>
+        <v>20.627810886015787</v>
       </c>
       <c r="V14" s="0">
-        <v>19.191580669670245</v>
+        <v>18.391472192291442</v>
       </c>
       <c r="W14" s="0">
-        <v>17.301479815795904</v>
+        <v>16.669293315034842</v>
       </c>
       <c r="X14" s="0">
-        <v>16.040210840602853</v>
+        <v>15.529735172450936</v>
       </c>
       <c r="Y14" s="0">
-        <v>15.179034109199293</v>
+        <v>14.75507489251823</v>
       </c>
       <c r="Z14" s="0">
-        <v>14.616380636478995</v>
+        <v>14.250172943906813</v>
       </c>
       <c r="AA14" s="0">
-        <v>14.238997624620346</v>
+        <v>13.909804533457264</v>
       </c>
       <c r="AB14" s="0">
-        <v>13.969352632833701</v>
+        <v>13.664766931450474</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>29.041580651196657</v>
+        <v>56.428959806049726</v>
       </c>
       <c r="B15" s="0">
-        <v>35.355303439080238</v>
+        <v>53.606561742358551</v>
       </c>
       <c r="C15" s="0">
-        <v>43.075429852859138</v>
+        <v>50.680813812558284</v>
       </c>
       <c r="D15" s="0">
-        <v>58.678480244564689</v>
+        <v>47.744003987371933</v>
       </c>
       <c r="E15" s="0">
-        <v>55.790058848714153</v>
+        <v>45.090496277587995</v>
       </c>
       <c r="F15" s="0">
-        <v>53.306451851318258</v>
+        <v>42.889078061999882</v>
       </c>
       <c r="G15" s="0">
-        <v>50.997547755721989</v>
+        <v>40.863186783620286</v>
       </c>
       <c r="H15" s="0">
-        <v>49.18680524046146</v>
+        <v>39.37556043289932</v>
       </c>
       <c r="I15" s="0">
-        <v>48.818985038749489</v>
+        <v>39.533977733903953</v>
       </c>
       <c r="J15" s="0">
-        <v>49.892425513627138</v>
+        <v>41.300005003446614</v>
       </c>
       <c r="K15" s="0">
-        <v>50.795212376069358</v>
+        <v>42.760129982481999</v>
       </c>
       <c r="L15" s="0">
-        <v>50.75972414013193</v>
+        <v>42.991787121062664</v>
       </c>
       <c r="M15" s="0">
-        <v>50.631770892138903</v>
+        <v>43.065809228342907</v>
       </c>
       <c r="N15" s="0">
-        <v>50.492195608615774</v>
+        <v>43.089806203797629</v>
       </c>
       <c r="O15" s="0">
-        <v>49.500099991542797</v>
+        <v>42.358685590383793</v>
       </c>
       <c r="P15" s="0">
-        <v>47.078859550820155</v>
+        <v>40.40931683511203</v>
       </c>
       <c r="Q15" s="0">
-        <v>43.6459747603135</v>
+        <v>37.615750877400608</v>
       </c>
       <c r="R15" s="0">
-        <v>39.611807726115892</v>
+        <v>34.330435921803584</v>
       </c>
       <c r="S15" s="0">
-        <v>35.343967099251948</v>
+        <v>30.859534044054048</v>
       </c>
       <c r="T15" s="0">
-        <v>31.13956545018371</v>
+        <v>27.444093340875014</v>
       </c>
       <c r="U15" s="0">
-        <v>27.21149512428978</v>
+        <v>24.25257760915191</v>
       </c>
       <c r="V15" s="0">
-        <v>23.689171709607191</v>
+        <v>21.384509040478413</v>
       </c>
       <c r="W15" s="0">
-        <v>20.964099167308799</v>
+        <v>19.183863938288031</v>
       </c>
       <c r="X15" s="0">
-        <v>19.097919541320987</v>
+        <v>17.705112947185004</v>
       </c>
       <c r="Y15" s="0">
-        <v>17.796362457200981</v>
+        <v>16.68942433164634</v>
       </c>
       <c r="Z15" s="0">
-        <v>16.875482409263739</v>
+        <v>15.979736653986375</v>
       </c>
       <c r="AA15" s="0">
-        <v>16.215749588675372</v>
+        <v>15.476246190023289</v>
       </c>
       <c r="AB15" s="0">
-        <v>15.737334888188682</v>
+        <v>15.113496580118593</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="0">
-        <v>28.991876462227889</v>
+        <v>37.683337917498449</v>
       </c>
       <c r="B16" s="0">
-        <v>35.314143369224325</v>
+        <v>35.400571542032573</v>
       </c>
       <c r="C16" s="0">
-        <v>43.03324892534436</v>
+        <v>33.103073730970891</v>
       </c>
       <c r="D16" s="0">
-        <v>33.565244618504586</v>
+        <v>30.861929556563393</v>
       </c>
       <c r="E16" s="0">
-        <v>31.473904670803133</v>
+        <v>28.928915608686307</v>
       </c>
       <c r="F16" s="0">
-        <v>29.836865431113235</v>
+        <v>27.423305541630615</v>
       </c>
       <c r="G16" s="0">
-        <v>28.377819701122913</v>
+        <v>26.063131162241565</v>
       </c>
       <c r="H16" s="0">
-        <v>27.43406174055001</v>
+        <v>25.205593701152637</v>
       </c>
       <c r="I16" s="0">
-        <v>27.88262141718684</v>
+        <v>25.801989711198452</v>
       </c>
       <c r="J16" s="0">
-        <v>29.58408386692367</v>
+        <v>27.671437396570074</v>
       </c>
       <c r="K16" s="0">
-        <v>30.840204988194199</v>
+        <v>28.984382012090567</v>
       </c>
       <c r="L16" s="0">
-        <v>31.050654175000563</v>
+        <v>29.095677223306012</v>
       </c>
       <c r="M16" s="0">
-        <v>31.13356700217944</v>
+        <v>29.0967738108126</v>
       </c>
       <c r="N16" s="0">
-        <v>31.175178156233972</v>
+        <v>29.078209126236914</v>
       </c>
       <c r="O16" s="0">
-        <v>30.662017594844098</v>
+        <v>28.551036928527193</v>
       </c>
       <c r="P16" s="0">
-        <v>29.2691837990767</v>
+        <v>27.214916729456426</v>
       </c>
       <c r="Q16" s="0">
-        <v>27.274950417441474</v>
+        <v>25.339179177072556</v>
       </c>
       <c r="R16" s="0">
-        <v>24.934263959984744</v>
+        <v>23.160505702315408</v>
       </c>
       <c r="S16" s="0">
-        <v>22.465622589153501</v>
+        <v>20.876784970152602</v>
       </c>
       <c r="T16" s="0">
-        <v>20.038704657182691</v>
+        <v>18.63941581264622</v>
       </c>
       <c r="U16" s="0">
-        <v>17.770219051943062</v>
+        <v>16.551373096975205</v>
       </c>
       <c r="V16" s="0">
-        <v>15.727712829652333</v>
+        <v>14.671509082926043</v>
       </c>
       <c r="W16" s="0">
-        <v>14.167383542288391</v>
+        <v>13.239964597586823</v>
       </c>
       <c r="X16" s="0">
-        <v>13.127966668665564</v>
+        <v>12.293005898385479</v>
       </c>
       <c r="Y16" s="0">
-        <v>12.417329265875578</v>
+        <v>11.646627418620412</v>
       </c>
       <c r="Z16" s="0">
-        <v>11.921370576106309</v>
+        <v>11.195013066993607</v>
       </c>
       <c r="AA16" s="0">
-        <v>11.568088834072359</v>
+        <v>10.872571998815962</v>
       </c>
       <c r="AB16" s="0">
-        <v>11.310702646578021</v>
+        <v>10.636942436525084</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="0">
-        <v>28.93400420653397</v>
+        <v>46.351282985848357</v>
       </c>
       <c r="B17" s="0">
-        <v>35.260664447828518</v>
+        <v>43.764925173661794</v>
       </c>
       <c r="C17" s="0">
-        <v>42.971980256157678</v>
+        <v>41.123488317495223</v>
       </c>
       <c r="D17" s="0">
-        <v>41.20888822405874</v>
+        <v>38.510576210699163</v>
       </c>
       <c r="E17" s="0">
-        <v>38.830695302346996</v>
+        <v>36.205261583571499</v>
       </c>
       <c r="F17" s="0">
-        <v>36.908102291564838</v>
+        <v>34.354622197488254</v>
       </c>
       <c r="G17" s="0">
-        <v>35.167775912987288</v>
+        <v>32.675601816306042</v>
       </c>
       <c r="H17" s="0">
-        <v>33.952432071429953</v>
+        <v>31.527029181394987</v>
       </c>
       <c r="I17" s="0">
-        <v>34.240968730004724</v>
+        <v>31.928556550407951</v>
       </c>
       <c r="J17" s="0">
-        <v>35.981644453177864</v>
+        <v>33.773763107886481</v>
       </c>
       <c r="K17" s="0">
-        <v>37.416258318344987</v>
+        <v>35.166742623144827</v>
       </c>
       <c r="L17" s="0">
-        <v>37.528077338803236</v>
+        <v>35.33660155240279</v>
       </c>
       <c r="M17" s="0">
-        <v>37.535062996737239</v>
+        <v>35.373548696283137</v>
       </c>
       <c r="N17" s="0">
-        <v>37.51652700370601</v>
+        <v>35.37760926333231</v>
       </c>
       <c r="O17" s="0">
-        <v>36.859599011110213</v>
+        <v>34.75381319221556</v>
       </c>
       <c r="P17" s="0">
-        <v>35.173056985865607</v>
+        <v>33.115140135198487</v>
       </c>
       <c r="Q17" s="0">
-        <v>32.711062776463969</v>
+        <v>30.778277959660969</v>
       </c>
       <c r="R17" s="0">
-        <v>29.785734735809754</v>
+        <v>28.03629421775036</v>
       </c>
       <c r="S17" s="0">
-        <v>26.674782502144275</v>
+        <v>25.14280406811665</v>
       </c>
       <c r="T17" s="0">
-        <v>23.600563868716598</v>
+        <v>22.296960133858036</v>
       </c>
       <c r="U17" s="0">
-        <v>20.720544072876297</v>
+        <v>19.637417794798168</v>
       </c>
       <c r="V17" s="0">
-        <v>18.125088007513206</v>
+        <v>17.245554797289142</v>
       </c>
       <c r="W17" s="0">
-        <v>16.087119924462329</v>
+        <v>15.37354363440889</v>
       </c>
       <c r="X17" s="0">
-        <v>14.69850680290903</v>
+        <v>14.108595935817405</v>
       </c>
       <c r="Y17" s="0">
-        <v>13.73282852078923</v>
+        <v>13.232824132046149</v>
       </c>
       <c r="Z17" s="0">
-        <v>13.050735737696698</v>
+        <v>12.632934820985971</v>
       </c>
       <c r="AA17" s="0">
-        <v>12.561703150814377</v>
+        <v>12.228183693129395</v>
       </c>
       <c r="AB17" s="0">
-        <v>12.208654960080009</v>
+        <v>11.93191101428012</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>28.871864422532443</v>
+        <v>56.428959806049726</v>
       </c>
       <c r="B18" s="0">
-        <v>35.199923006784616</v>
+        <v>53.606561742358551</v>
       </c>
       <c r="C18" s="0">
-        <v>42.898348470474737</v>
+        <v>50.680813812558284</v>
       </c>
       <c r="D18" s="0">
-        <v>58.678480244564689</v>
+        <v>47.744003987371933</v>
       </c>
       <c r="E18" s="0">
-        <v>55.790058848714153</v>
+        <v>45.090496277587995</v>
       </c>
       <c r="F18" s="0">
-        <v>53.306451851318258</v>
+        <v>42.889078061999882</v>
       </c>
       <c r="G18" s="0">
-        <v>50.997547755721989</v>
+        <v>40.863186783620286</v>
       </c>
       <c r="H18" s="0">
-        <v>49.18680524046146</v>
+        <v>39.37556043289932</v>
       </c>
       <c r="I18" s="0">
-        <v>48.818985038749489</v>
+        <v>39.533977733903953</v>
       </c>
       <c r="J18" s="0">
-        <v>49.892425513627138</v>
+        <v>41.300005003446614</v>
       </c>
       <c r="K18" s="0">
-        <v>50.795212376069358</v>
+        <v>42.760129982481999</v>
       </c>
       <c r="L18" s="0">
-        <v>50.75972414013193</v>
+        <v>42.991787121062664</v>
       </c>
       <c r="M18" s="0">
-        <v>50.631770892138903</v>
+        <v>43.065809228342907</v>
       </c>
       <c r="N18" s="0">
-        <v>50.492206062410148</v>
+        <v>43.089830857847908</v>
       </c>
       <c r="O18" s="0">
-        <v>49.484441564373562</v>
+        <v>42.336868995330264</v>
       </c>
       <c r="P18" s="0">
-        <v>47.004107535770906</v>
+        <v>40.30816511906513</v>
       </c>
       <c r="Q18" s="0">
-        <v>43.461042302636358</v>
+        <v>37.37364314401141</v>
       </c>
       <c r="R18" s="0">
-        <v>39.27039499074197</v>
+        <v>33.894633601178285</v>
       </c>
       <c r="S18" s="0">
-        <v>34.814357220905997</v>
+        <v>30.196023339190553</v>
       </c>
       <c r="T18" s="0">
-        <v>30.408660616099745</v>
+        <v>26.54105586888166</v>
       </c>
       <c r="U18" s="0">
-        <v>26.284098514188301</v>
+        <v>23.118469317581315</v>
       </c>
       <c r="V18" s="0">
-        <v>22.584019068721165</v>
+        <v>20.042956778854109</v>
       </c>
       <c r="W18" s="0">
-        <v>19.701370328931336</v>
+        <v>17.661296445398502</v>
       </c>
       <c r="X18" s="0">
-        <v>17.697714758817941</v>
+        <v>16.029910519917948</v>
       </c>
       <c r="Y18" s="0">
-        <v>16.281403880772601</v>
+        <v>14.890015703910096</v>
       </c>
       <c r="Z18" s="0">
-        <v>15.26731898230592</v>
+        <v>14.081801914863759</v>
       </c>
       <c r="AA18" s="0">
-        <v>14.532665433042753</v>
+        <v>13.500954110093931</v>
       </c>
       <c r="AB18" s="0">
-        <v>13.993959499691625</v>
+        <v>13.077389378476257</v>
       </c>
     </row>
     <row r="19">
